--- a/VerveStacks_FRA_grids_kan25/SysSettings.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SysSettings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_FRA_grids_kan25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{124E6D3A-FC03-4295-B842-4EF01612E4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF10642-36A7-4A17-B5C4-3EF15813657D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -1217,160 +1217,160 @@
     <t>e_w110086345-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/110086345-400</t>
-  </si>
-  <si>
     <t>lo</t>
   </si>
   <si>
     <t>e_w111558550-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/111558550-400</t>
-  </si>
-  <si>
     <t>e_w112342683-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/112342683-400</t>
-  </si>
-  <si>
     <t>e_w118086309-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/118086309-400</t>
-  </si>
-  <si>
     <t>e_w146695955-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/146695955-400</t>
-  </si>
-  <si>
     <t>e_w147132694-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/147132694-400</t>
-  </si>
-  <si>
     <t>e_w159167277-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/159167277-400</t>
-  </si>
-  <si>
     <t>e_w179260933-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/179260933-400</t>
-  </si>
-  <si>
     <t>e_w235370803-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/235370803-400</t>
-  </si>
-  <si>
     <t>e_w24020601-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/24020601-400</t>
-  </si>
-  <si>
     <t>e_w27259817-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/27259817-400</t>
-  </si>
-  <si>
     <t>e_w36805588-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/36805588-400</t>
-  </si>
-  <si>
     <t>e_w49510896-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/49510896-400</t>
-  </si>
-  <si>
     <t>e_w71933077-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/71933077-400</t>
-  </si>
-  <si>
     <t>e_w79866837-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/79866837-400</t>
-  </si>
-  <si>
     <t>e_w81641090-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/81641090-400</t>
-  </si>
-  <si>
     <t>e_w82599261-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/82599261-400</t>
-  </si>
-  <si>
     <t>e_w82825438-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/82825438-400</t>
-  </si>
-  <si>
     <t>e_w85047359-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/85047359-400</t>
-  </si>
-  <si>
     <t>e_w85203486-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/85203486-400</t>
-  </si>
-  <si>
     <t>e_w85605950-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/85605950-400</t>
-  </si>
-  <si>
     <t>e_w85710783-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/85710783-400</t>
-  </si>
-  <si>
     <t>e_w85995894-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/85995894-400</t>
-  </si>
-  <si>
     <t>e_w90842395-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/90842395-400</t>
-  </si>
-  <si>
     <t>e_w98890904-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/98890904-400</t>
-  </si>
-  <si>
     <t>e_w99722046-400_FRA</t>
   </si>
   <si>
-    <t>grid node -- way/99722046-400</t>
+    <t>grid node -- way/110086345-400 (Nimes, 30 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/111558550-400 (Bayonne, 9 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/112342683-400 (Nantes, 25 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/118086309-400 (Strasbourg, 16 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/146695955-400 (Brest, 23 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/147132694-400 (Grenoble, 26 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/159167277-400 (Besancon, 42 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/179260933-400 (Dijon, 25 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/235370803-400 (Bordeaux, 28 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/24020601-400 (Lyon, 24 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/27259817-400 (Marseille, 17 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/36805588-400 (Amiens, 6 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/49510896-400 (Toulouse, 27 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/71933077-400 (Clermont-Ferrand, 15 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/79866837-400 (Paris, 64 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/81641090-400 (Metz, 11 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/82599261-400 (Troyes, 27 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/82825438-400 (Reims, 74 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/85047359-400 (Paris, 41 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/85203486-400 (Dunkerque, 18 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/85605950-400 (Lille, 12 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/85710783-400 (Rouen, 24 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/85995894-400 (Rennes, 9 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/90842395-400 (Nice, 13 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/98890904-400 (Beziers, 45 km)</t>
+  </si>
+  <si>
+    <t>grid node -- way/99722046-400 (Angers, 44 km)</t>
   </si>
 </sst>
 </file>
@@ -6224,713 +6224,717 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B511CD34-B5BA-48DA-805B-066700D1B1E6}">
-  <dimension ref="B3:I30"/>
+  <dimension ref="C3:J30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="4" max="4" width="20.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:9">
-      <c r="B3" t="s">
+    <row r="3" spans="3:10">
+      <c r="C3" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
-      <c r="B4" t="s">
+    <row r="4" spans="3:10">
+      <c r="C4" t="s">
         <v>218</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>238</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>15</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
+    <row r="5" spans="3:10">
       <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>391</v>
       </c>
-      <c r="D5" t="s">
-        <v>237</v>
-      </c>
       <c r="E5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F5" t="s">
+        <v>418</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
         <v>392</v>
       </c>
-      <c r="F5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="J5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10">
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
         <v>393</v>
       </c>
-      <c r="I5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F6" t="s">
+        <v>419</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>392</v>
+      </c>
+      <c r="J6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10">
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
         <v>394</v>
       </c>
-      <c r="D6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F7" t="s">
+        <v>420</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" t="s">
+        <v>392</v>
+      </c>
+      <c r="J7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10">
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
         <v>395</v>
       </c>
-      <c r="F6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" t="s">
-        <v>393</v>
-      </c>
-      <c r="I6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E8" t="s">
+        <v>237</v>
+      </c>
+      <c r="F8" t="s">
+        <v>421</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
+        <v>392</v>
+      </c>
+      <c r="J8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10">
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" t="s">
         <v>396</v>
       </c>
-      <c r="D7" t="s">
-        <v>237</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="E9" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" t="s">
+        <v>422</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s">
+        <v>392</v>
+      </c>
+      <c r="J9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
         <v>397</v>
       </c>
-      <c r="F7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>393</v>
-      </c>
-      <c r="I7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9">
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F10" t="s">
+        <v>423</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
+        <v>392</v>
+      </c>
+      <c r="J10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10">
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
         <v>398</v>
       </c>
-      <c r="D8" t="s">
-        <v>237</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="E11" t="s">
+        <v>237</v>
+      </c>
+      <c r="F11" t="s">
+        <v>424</v>
+      </c>
+      <c r="G11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" t="s">
+        <v>392</v>
+      </c>
+      <c r="J11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10">
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
         <v>399</v>
       </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" t="s">
-        <v>393</v>
-      </c>
-      <c r="I8" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E12" t="s">
+        <v>237</v>
+      </c>
+      <c r="F12" t="s">
+        <v>425</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12" t="s">
+        <v>392</v>
+      </c>
+      <c r="J12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10">
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
         <v>400</v>
       </c>
-      <c r="D9" t="s">
-        <v>237</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="E13" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" t="s">
+        <v>426</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I13" t="s">
+        <v>392</v>
+      </c>
+      <c r="J13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="3:10">
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
         <v>401</v>
       </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" t="s">
-        <v>393</v>
-      </c>
-      <c r="I9" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="E14" t="s">
+        <v>237</v>
+      </c>
+      <c r="F14" t="s">
+        <v>427</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" t="s">
+        <v>35</v>
+      </c>
+      <c r="I14" t="s">
+        <v>392</v>
+      </c>
+      <c r="J14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="3:10">
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
         <v>402</v>
       </c>
-      <c r="D10" t="s">
-        <v>237</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="E15" t="s">
+        <v>237</v>
+      </c>
+      <c r="F15" t="s">
+        <v>428</v>
+      </c>
+      <c r="G15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" t="s">
+        <v>392</v>
+      </c>
+      <c r="J15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10">
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
         <v>403</v>
       </c>
-      <c r="F10" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" t="s">
-        <v>393</v>
-      </c>
-      <c r="I10" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="E16" t="s">
+        <v>237</v>
+      </c>
+      <c r="F16" t="s">
+        <v>429</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>392</v>
+      </c>
+      <c r="J16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10">
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
         <v>404</v>
       </c>
-      <c r="D11" t="s">
-        <v>237</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="E17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F17" t="s">
+        <v>430</v>
+      </c>
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" t="s">
+        <v>392</v>
+      </c>
+      <c r="J17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10">
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" t="s">
         <v>405</v>
       </c>
-      <c r="F11" t="s">
-        <v>25</v>
-      </c>
-      <c r="G11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" t="s">
-        <v>393</v>
-      </c>
-      <c r="I11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="12" spans="2:9">
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="E18" t="s">
+        <v>237</v>
+      </c>
+      <c r="F18" t="s">
+        <v>431</v>
+      </c>
+      <c r="G18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" t="s">
+        <v>392</v>
+      </c>
+      <c r="J18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="3:10">
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" t="s">
         <v>406</v>
       </c>
-      <c r="D12" t="s">
-        <v>237</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="E19" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" t="s">
+        <v>432</v>
+      </c>
+      <c r="G19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" t="s">
+        <v>392</v>
+      </c>
+      <c r="J19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10">
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" t="s">
         <v>407</v>
       </c>
-      <c r="F12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>393</v>
-      </c>
-      <c r="I12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="E20" t="s">
+        <v>237</v>
+      </c>
+      <c r="F20" t="s">
+        <v>433</v>
+      </c>
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" t="s">
+        <v>392</v>
+      </c>
+      <c r="J20" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10">
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
         <v>408</v>
       </c>
-      <c r="D13" t="s">
-        <v>237</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="E21" t="s">
+        <v>237</v>
+      </c>
+      <c r="F21" t="s">
+        <v>434</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" t="s">
+        <v>392</v>
+      </c>
+      <c r="J21" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10">
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" t="s">
         <v>409</v>
       </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" t="s">
-        <v>35</v>
-      </c>
-      <c r="H13" t="s">
-        <v>393</v>
-      </c>
-      <c r="I13" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9">
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="E22" t="s">
+        <v>237</v>
+      </c>
+      <c r="F22" t="s">
+        <v>435</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" t="s">
+        <v>392</v>
+      </c>
+      <c r="J22" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10">
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
         <v>410</v>
       </c>
-      <c r="D14" t="s">
-        <v>237</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="E23" t="s">
+        <v>237</v>
+      </c>
+      <c r="F23" t="s">
+        <v>436</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" t="s">
+        <v>392</v>
+      </c>
+      <c r="J23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10">
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
         <v>411</v>
       </c>
-      <c r="F14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" t="s">
-        <v>393</v>
-      </c>
-      <c r="I14" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="B15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="E24" t="s">
+        <v>237</v>
+      </c>
+      <c r="F24" t="s">
+        <v>437</v>
+      </c>
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" t="s">
+        <v>392</v>
+      </c>
+      <c r="J24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10">
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" t="s">
         <v>412</v>
       </c>
-      <c r="D15" t="s">
-        <v>237</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="E25" t="s">
+        <v>237</v>
+      </c>
+      <c r="F25" t="s">
+        <v>438</v>
+      </c>
+      <c r="G25" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" t="s">
+        <v>392</v>
+      </c>
+      <c r="J25" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10">
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" t="s">
         <v>413</v>
       </c>
-      <c r="F15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G15" t="s">
-        <v>35</v>
-      </c>
-      <c r="H15" t="s">
-        <v>393</v>
-      </c>
-      <c r="I15" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="E26" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" t="s">
+        <v>439</v>
+      </c>
+      <c r="G26" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" t="s">
+        <v>392</v>
+      </c>
+      <c r="J26" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10">
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
         <v>414</v>
       </c>
-      <c r="D16" t="s">
-        <v>237</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="E27" t="s">
+        <v>237</v>
+      </c>
+      <c r="F27" t="s">
+        <v>440</v>
+      </c>
+      <c r="G27" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" t="s">
+        <v>392</v>
+      </c>
+      <c r="J27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10">
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" t="s">
         <v>415</v>
       </c>
-      <c r="F16" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" t="s">
-        <v>393</v>
-      </c>
-      <c r="I16" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="E28" t="s">
+        <v>237</v>
+      </c>
+      <c r="F28" t="s">
+        <v>441</v>
+      </c>
+      <c r="G28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" t="s">
+        <v>35</v>
+      </c>
+      <c r="I28" t="s">
+        <v>392</v>
+      </c>
+      <c r="J28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10">
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" t="s">
         <v>416</v>
       </c>
-      <c r="D17" t="s">
-        <v>237</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="E29" t="s">
+        <v>237</v>
+      </c>
+      <c r="F29" t="s">
+        <v>442</v>
+      </c>
+      <c r="G29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" t="s">
+        <v>35</v>
+      </c>
+      <c r="I29" t="s">
+        <v>392</v>
+      </c>
+      <c r="J29" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10">
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
         <v>417</v>
       </c>
-      <c r="F17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" t="s">
-        <v>393</v>
-      </c>
-      <c r="I17" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
-        <v>418</v>
-      </c>
-      <c r="D18" t="s">
-        <v>237</v>
-      </c>
-      <c r="E18" t="s">
-        <v>419</v>
-      </c>
-      <c r="F18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" t="s">
-        <v>35</v>
-      </c>
-      <c r="H18" t="s">
-        <v>393</v>
-      </c>
-      <c r="I18" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>420</v>
-      </c>
-      <c r="D19" t="s">
-        <v>237</v>
-      </c>
-      <c r="E19" t="s">
-        <v>421</v>
-      </c>
-      <c r="F19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" t="s">
-        <v>35</v>
-      </c>
-      <c r="H19" t="s">
-        <v>393</v>
-      </c>
-      <c r="I19" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" t="s">
-        <v>422</v>
-      </c>
-      <c r="D20" t="s">
-        <v>237</v>
-      </c>
-      <c r="E20" t="s">
-        <v>423</v>
-      </c>
-      <c r="F20" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" t="s">
-        <v>393</v>
-      </c>
-      <c r="I20" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" t="s">
-        <v>424</v>
-      </c>
-      <c r="D21" t="s">
-        <v>237</v>
-      </c>
-      <c r="E21" t="s">
-        <v>425</v>
-      </c>
-      <c r="F21" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H21" t="s">
-        <v>393</v>
-      </c>
-      <c r="I21" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" t="s">
-        <v>426</v>
-      </c>
-      <c r="D22" t="s">
-        <v>237</v>
-      </c>
-      <c r="E22" t="s">
-        <v>427</v>
-      </c>
-      <c r="F22" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" t="s">
-        <v>35</v>
-      </c>
-      <c r="H22" t="s">
-        <v>393</v>
-      </c>
-      <c r="I22" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" t="s">
-        <v>428</v>
-      </c>
-      <c r="D23" t="s">
-        <v>237</v>
-      </c>
-      <c r="E23" t="s">
-        <v>429</v>
-      </c>
-      <c r="F23" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" t="s">
-        <v>393</v>
-      </c>
-      <c r="I23" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" t="s">
-        <v>430</v>
-      </c>
-      <c r="D24" t="s">
-        <v>237</v>
-      </c>
-      <c r="E24" t="s">
-        <v>431</v>
-      </c>
-      <c r="F24" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" t="s">
-        <v>393</v>
-      </c>
-      <c r="I24" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>432</v>
-      </c>
-      <c r="D25" t="s">
-        <v>237</v>
-      </c>
-      <c r="E25" t="s">
-        <v>433</v>
-      </c>
-      <c r="F25" t="s">
-        <v>25</v>
-      </c>
-      <c r="G25" t="s">
-        <v>35</v>
-      </c>
-      <c r="H25" t="s">
-        <v>393</v>
-      </c>
-      <c r="I25" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" t="s">
-        <v>434</v>
-      </c>
-      <c r="D26" t="s">
-        <v>237</v>
-      </c>
-      <c r="E26" t="s">
-        <v>435</v>
-      </c>
-      <c r="F26" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" t="s">
-        <v>35</v>
-      </c>
-      <c r="H26" t="s">
-        <v>393</v>
-      </c>
-      <c r="I26" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" t="s">
-        <v>436</v>
-      </c>
-      <c r="D27" t="s">
-        <v>237</v>
-      </c>
-      <c r="E27" t="s">
-        <v>437</v>
-      </c>
-      <c r="F27" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" t="s">
-        <v>35</v>
-      </c>
-      <c r="H27" t="s">
-        <v>393</v>
-      </c>
-      <c r="I27" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9">
-      <c r="B28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" t="s">
-        <v>438</v>
-      </c>
-      <c r="D28" t="s">
-        <v>237</v>
-      </c>
-      <c r="E28" t="s">
-        <v>439</v>
-      </c>
-      <c r="F28" t="s">
-        <v>25</v>
-      </c>
-      <c r="G28" t="s">
-        <v>35</v>
-      </c>
-      <c r="H28" t="s">
-        <v>393</v>
-      </c>
-      <c r="I28" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9">
-      <c r="B29" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" t="s">
-        <v>440</v>
-      </c>
-      <c r="D29" t="s">
-        <v>237</v>
-      </c>
-      <c r="E29" t="s">
-        <v>441</v>
-      </c>
-      <c r="F29" t="s">
-        <v>25</v>
-      </c>
-      <c r="G29" t="s">
-        <v>35</v>
-      </c>
-      <c r="H29" t="s">
-        <v>393</v>
-      </c>
-      <c r="I29" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9">
-      <c r="B30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" t="s">
-        <v>442</v>
-      </c>
-      <c r="D30" t="s">
-        <v>237</v>
-      </c>
       <c r="E30" t="s">
+        <v>237</v>
+      </c>
+      <c r="F30" t="s">
         <v>443</v>
       </c>
-      <c r="F30" t="s">
-        <v>25</v>
-      </c>
       <c r="G30" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H30" t="s">
-        <v>393</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
+        <v>392</v>
+      </c>
+      <c r="J30" t="s">
         <v>241</v>
       </c>
     </row>

--- a/VerveStacks_FRA_grids_kan25/SysSettings.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SysSettings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_FRA_grids_kan25\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF10642-36A7-4A17-B5C4-3EF15813657D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC27E40-D542-4407-9376-32DC514A3EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="system_settings" sheetId="1" r:id="rId1"/>
@@ -1217,157 +1217,157 @@
     <t>e_w110086345-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/110086345-400 (Nimes, 30 km)</t>
+  </si>
+  <si>
     <t>lo</t>
   </si>
   <si>
     <t>e_w111558550-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/111558550-400 (Bayonne, 9 km)</t>
+  </si>
+  <si>
     <t>e_w112342683-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/112342683-400 (Nantes, 25 km)</t>
+  </si>
+  <si>
     <t>e_w118086309-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/118086309-400 (Strasbourg, 16 km)</t>
+  </si>
+  <si>
     <t>e_w146695955-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/146695955-400 (Brest, 23 km)</t>
+  </si>
+  <si>
     <t>e_w147132694-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/147132694-400 (Grenoble, 26 km)</t>
+  </si>
+  <si>
     <t>e_w159167277-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/159167277-400 (Besancon, 42 km)</t>
+  </si>
+  <si>
     <t>e_w179260933-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/179260933-400 (Dijon, 25 km)</t>
+  </si>
+  <si>
     <t>e_w235370803-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/235370803-400 (Bordeaux, 28 km)</t>
+  </si>
+  <si>
     <t>e_w24020601-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/24020601-400 (Lyon, 24 km)</t>
+  </si>
+  <si>
     <t>e_w27259817-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/27259817-400 (Marseille, 17 km)</t>
+  </si>
+  <si>
     <t>e_w36805588-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/36805588-400 (Amiens, 6 km)</t>
+  </si>
+  <si>
     <t>e_w49510896-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/49510896-400 (Toulouse, 27 km)</t>
+  </si>
+  <si>
     <t>e_w71933077-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/71933077-400 (Clermont-Ferrand, 15 km)</t>
+  </si>
+  <si>
     <t>e_w79866837-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/79866837-400 (Paris, 64 km)</t>
+  </si>
+  <si>
     <t>e_w81641090-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/81641090-400 (Metz, 11 km)</t>
+  </si>
+  <si>
     <t>e_w82599261-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/82599261-400 (Troyes, 27 km)</t>
+  </si>
+  <si>
     <t>e_w82825438-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/82825438-400 (Reims, 74 km)</t>
+  </si>
+  <si>
     <t>e_w85047359-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/85047359-400 (Paris, 41 km)</t>
+  </si>
+  <si>
     <t>e_w85203486-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/85203486-400 (Dunkerque, 18 km)</t>
+  </si>
+  <si>
     <t>e_w85605950-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/85605950-400 (Lille, 12 km)</t>
+  </si>
+  <si>
     <t>e_w85710783-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/85710783-400 (Rouen, 24 km)</t>
+  </si>
+  <si>
     <t>e_w85995894-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/85995894-400 (Rennes, 9 km)</t>
+  </si>
+  <si>
     <t>e_w90842395-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/90842395-400 (Nice, 13 km)</t>
+  </si>
+  <si>
     <t>e_w98890904-400_FRA</t>
   </si>
   <si>
+    <t>grid node -- way/98890904-400 (Beziers, 45 km)</t>
+  </si>
+  <si>
     <t>e_w99722046-400_FRA</t>
-  </si>
-  <si>
-    <t>grid node -- way/110086345-400 (Nimes, 30 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/111558550-400 (Bayonne, 9 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/112342683-400 (Nantes, 25 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/118086309-400 (Strasbourg, 16 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/146695955-400 (Brest, 23 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/147132694-400 (Grenoble, 26 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/159167277-400 (Besancon, 42 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/179260933-400 (Dijon, 25 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/235370803-400 (Bordeaux, 28 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/24020601-400 (Lyon, 24 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/27259817-400 (Marseille, 17 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/36805588-400 (Amiens, 6 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/49510896-400 (Toulouse, 27 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/71933077-400 (Clermont-Ferrand, 15 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/79866837-400 (Paris, 64 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/81641090-400 (Metz, 11 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/82599261-400 (Troyes, 27 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/82825438-400 (Reims, 74 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/85047359-400 (Paris, 41 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/85203486-400 (Dunkerque, 18 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/85605950-400 (Lille, 12 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/85710783-400 (Rouen, 24 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/85995894-400 (Rennes, 9 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/90842395-400 (Nice, 13 km)</t>
-  </si>
-  <si>
-    <t>grid node -- way/98890904-400 (Beziers, 45 km)</t>
   </si>
   <si>
     <t>grid node -- way/99722046-400 (Angers, 44 km)</t>
@@ -6223,718 +6223,714 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B511CD34-B5BA-48DA-805B-066700D1B1E6}">
-  <dimension ref="C3:J30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB30AB0-9DED-4762-9CEF-0BA57B65D439}">
+  <dimension ref="B3:I30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="4" max="4" width="20.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="3" spans="3:10">
-      <c r="C3" t="s">
+    <row r="3" spans="2:9">
+      <c r="B3" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="4" spans="3:10">
+    <row r="4" spans="2:9">
+      <c r="B4" t="s">
+        <v>218</v>
+      </c>
       <c r="C4" t="s">
-        <v>218</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>238</v>
       </c>
       <c r="E4" t="s">
-        <v>238</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="3:10">
+    <row r="5" spans="2:9">
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>391</v>
       </c>
       <c r="D5" t="s">
-        <v>391</v>
+        <v>237</v>
       </c>
       <c r="E5" t="s">
-        <v>237</v>
+        <v>392</v>
       </c>
       <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>393</v>
+      </c>
+      <c r="I5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>394</v>
+      </c>
+      <c r="D6" t="s">
+        <v>237</v>
+      </c>
+      <c r="E6" t="s">
+        <v>395</v>
+      </c>
+      <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>393</v>
+      </c>
+      <c r="I6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>396</v>
+      </c>
+      <c r="D7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E7" t="s">
+        <v>397</v>
+      </c>
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>393</v>
+      </c>
+      <c r="I7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>398</v>
+      </c>
+      <c r="D8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" t="s">
+        <v>399</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>393</v>
+      </c>
+      <c r="I8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" t="s">
+        <v>401</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>393</v>
+      </c>
+      <c r="I9" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10" t="s">
+        <v>237</v>
+      </c>
+      <c r="E10" t="s">
+        <v>403</v>
+      </c>
+      <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>393</v>
+      </c>
+      <c r="I10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>404</v>
+      </c>
+      <c r="D11" t="s">
+        <v>237</v>
+      </c>
+      <c r="E11" t="s">
+        <v>405</v>
+      </c>
+      <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>393</v>
+      </c>
+      <c r="I11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>406</v>
+      </c>
+      <c r="D12" t="s">
+        <v>237</v>
+      </c>
+      <c r="E12" t="s">
+        <v>407</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>393</v>
+      </c>
+      <c r="I12" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>408</v>
+      </c>
+      <c r="D13" t="s">
+        <v>237</v>
+      </c>
+      <c r="E13" t="s">
+        <v>409</v>
+      </c>
+      <c r="F13" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>393</v>
+      </c>
+      <c r="I13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>410</v>
+      </c>
+      <c r="D14" t="s">
+        <v>237</v>
+      </c>
+      <c r="E14" t="s">
+        <v>411</v>
+      </c>
+      <c r="F14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
+        <v>393</v>
+      </c>
+      <c r="I14" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>412</v>
+      </c>
+      <c r="D15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" t="s">
+        <v>413</v>
+      </c>
+      <c r="F15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>393</v>
+      </c>
+      <c r="I15" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>414</v>
+      </c>
+      <c r="D16" t="s">
+        <v>237</v>
+      </c>
+      <c r="E16" t="s">
+        <v>415</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" t="s">
+        <v>393</v>
+      </c>
+      <c r="I16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>416</v>
+      </c>
+      <c r="D17" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" t="s">
+        <v>417</v>
+      </c>
+      <c r="F17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" t="s">
+        <v>393</v>
+      </c>
+      <c r="I17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
         <v>418</v>
       </c>
-      <c r="G5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s">
-        <v>392</v>
-      </c>
-      <c r="J5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="3:10">
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="D18" t="s">
+        <v>237</v>
+      </c>
+      <c r="E18" t="s">
+        <v>419</v>
+      </c>
+      <c r="F18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" t="s">
         <v>393</v>
       </c>
-      <c r="E6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" t="s">
-        <v>419</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>35</v>
-      </c>
-      <c r="I6" t="s">
-        <v>392</v>
-      </c>
-      <c r="J6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="7" spans="3:10">
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>394</v>
-      </c>
-      <c r="E7" t="s">
-        <v>237</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="I18" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
         <v>420</v>
       </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" t="s">
-        <v>392</v>
-      </c>
-      <c r="J7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="3:10">
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" t="s">
-        <v>395</v>
-      </c>
-      <c r="E8" t="s">
-        <v>237</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="D19" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" t="s">
         <v>421</v>
       </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" t="s">
-        <v>392</v>
-      </c>
-      <c r="J8" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="9" spans="3:10">
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" t="s">
-        <v>396</v>
-      </c>
-      <c r="E9" t="s">
-        <v>237</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" t="s">
+        <v>393</v>
+      </c>
+      <c r="I19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
         <v>422</v>
       </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" t="s">
-        <v>392</v>
-      </c>
-      <c r="J9" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="10" spans="3:10">
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>397</v>
-      </c>
-      <c r="E10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="D20" t="s">
+        <v>237</v>
+      </c>
+      <c r="E20" t="s">
         <v>423</v>
       </c>
-      <c r="G10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" t="s">
-        <v>392</v>
-      </c>
-      <c r="J10" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="11" spans="3:10">
-      <c r="C11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" t="s">
-        <v>398</v>
-      </c>
-      <c r="E11" t="s">
-        <v>237</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="F20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" t="s">
+        <v>393</v>
+      </c>
+      <c r="I20" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
         <v>424</v>
       </c>
-      <c r="G11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" t="s">
-        <v>392</v>
-      </c>
-      <c r="J11" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="12" spans="3:10">
-      <c r="C12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" t="s">
-        <v>399</v>
-      </c>
-      <c r="E12" t="s">
-        <v>237</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="D21" t="s">
+        <v>237</v>
+      </c>
+      <c r="E21" t="s">
         <v>425</v>
       </c>
-      <c r="G12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" t="s">
-        <v>392</v>
-      </c>
-      <c r="J12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="13" spans="3:10">
-      <c r="C13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" t="s">
-        <v>400</v>
-      </c>
-      <c r="E13" t="s">
-        <v>237</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="F21" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" t="s">
+        <v>393</v>
+      </c>
+      <c r="I21" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
         <v>426</v>
       </c>
-      <c r="G13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" t="s">
-        <v>35</v>
-      </c>
-      <c r="I13" t="s">
-        <v>392</v>
-      </c>
-      <c r="J13" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="14" spans="3:10">
-      <c r="C14" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" t="s">
-        <v>401</v>
-      </c>
-      <c r="E14" t="s">
-        <v>237</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="D22" t="s">
+        <v>237</v>
+      </c>
+      <c r="E22" t="s">
         <v>427</v>
       </c>
-      <c r="G14" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" t="s">
-        <v>35</v>
-      </c>
-      <c r="I14" t="s">
-        <v>392</v>
-      </c>
-      <c r="J14" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="15" spans="3:10">
-      <c r="C15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" t="s">
-        <v>402</v>
-      </c>
-      <c r="E15" t="s">
-        <v>237</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="F22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" t="s">
+        <v>393</v>
+      </c>
+      <c r="I22" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" t="s">
         <v>428</v>
       </c>
-      <c r="G15" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" t="s">
-        <v>392</v>
-      </c>
-      <c r="J15" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" spans="3:10">
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" t="s">
-        <v>403</v>
-      </c>
-      <c r="E16" t="s">
-        <v>237</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="D23" t="s">
+        <v>237</v>
+      </c>
+      <c r="E23" t="s">
         <v>429</v>
       </c>
-      <c r="G16" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" t="s">
-        <v>392</v>
-      </c>
-      <c r="J16" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="17" spans="3:10">
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" t="s">
-        <v>404</v>
-      </c>
-      <c r="E17" t="s">
-        <v>237</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" t="s">
+        <v>393</v>
+      </c>
+      <c r="I23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
         <v>430</v>
       </c>
-      <c r="G17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" t="s">
-        <v>392</v>
-      </c>
-      <c r="J17" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="18" spans="3:10">
-      <c r="C18" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" t="s">
-        <v>405</v>
-      </c>
-      <c r="E18" t="s">
-        <v>237</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="D24" t="s">
+        <v>237</v>
+      </c>
+      <c r="E24" t="s">
         <v>431</v>
       </c>
-      <c r="G18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" t="s">
-        <v>392</v>
-      </c>
-      <c r="J18" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="19" spans="3:10">
-      <c r="C19" t="s">
-        <v>17</v>
-      </c>
-      <c r="D19" t="s">
-        <v>406</v>
-      </c>
-      <c r="E19" t="s">
-        <v>237</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="F24" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" t="s">
+        <v>393</v>
+      </c>
+      <c r="I24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" t="s">
         <v>432</v>
       </c>
-      <c r="G19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" t="s">
-        <v>392</v>
-      </c>
-      <c r="J19" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="20" spans="3:10">
-      <c r="C20" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" t="s">
-        <v>407</v>
-      </c>
-      <c r="E20" t="s">
-        <v>237</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="D25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E25" t="s">
         <v>433</v>
       </c>
-      <c r="G20" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" t="s">
-        <v>392</v>
-      </c>
-      <c r="J20" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="3:10">
-      <c r="C21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" t="s">
-        <v>408</v>
-      </c>
-      <c r="E21" t="s">
-        <v>237</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="F25" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" t="s">
+        <v>393</v>
+      </c>
+      <c r="I25" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" t="s">
         <v>434</v>
       </c>
-      <c r="G21" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" t="s">
-        <v>35</v>
-      </c>
-      <c r="I21" t="s">
-        <v>392</v>
-      </c>
-      <c r="J21" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="22" spans="3:10">
-      <c r="C22" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" t="s">
-        <v>409</v>
-      </c>
-      <c r="E22" t="s">
-        <v>237</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="D26" t="s">
+        <v>237</v>
+      </c>
+      <c r="E26" t="s">
         <v>435</v>
       </c>
-      <c r="G22" t="s">
-        <v>25</v>
-      </c>
-      <c r="H22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" t="s">
-        <v>392</v>
-      </c>
-      <c r="J22" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="23" spans="3:10">
-      <c r="C23" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" t="s">
-        <v>410</v>
-      </c>
-      <c r="E23" t="s">
-        <v>237</v>
-      </c>
-      <c r="F23" t="s">
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" t="s">
+        <v>393</v>
+      </c>
+      <c r="I26" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" t="s">
         <v>436</v>
       </c>
-      <c r="G23" t="s">
-        <v>25</v>
-      </c>
-      <c r="H23" t="s">
-        <v>35</v>
-      </c>
-      <c r="I23" t="s">
-        <v>392</v>
-      </c>
-      <c r="J23" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="24" spans="3:10">
-      <c r="C24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" t="s">
-        <v>411</v>
-      </c>
-      <c r="E24" t="s">
-        <v>237</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="D27" t="s">
+        <v>237</v>
+      </c>
+      <c r="E27" t="s">
         <v>437</v>
       </c>
-      <c r="G24" t="s">
-        <v>25</v>
-      </c>
-      <c r="H24" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" t="s">
-        <v>392</v>
-      </c>
-      <c r="J24" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="25" spans="3:10">
-      <c r="C25" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" t="s">
-        <v>412</v>
-      </c>
-      <c r="E25" t="s">
-        <v>237</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="F27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" t="s">
+        <v>393</v>
+      </c>
+      <c r="I27" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" t="s">
         <v>438</v>
       </c>
-      <c r="G25" t="s">
-        <v>25</v>
-      </c>
-      <c r="H25" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" t="s">
-        <v>392</v>
-      </c>
-      <c r="J25" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="26" spans="3:10">
-      <c r="C26" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" t="s">
-        <v>413</v>
-      </c>
-      <c r="E26" t="s">
-        <v>237</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="D28" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" t="s">
         <v>439</v>
       </c>
-      <c r="G26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" t="s">
-        <v>35</v>
-      </c>
-      <c r="I26" t="s">
-        <v>392</v>
-      </c>
-      <c r="J26" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="27" spans="3:10">
-      <c r="C27" t="s">
-        <v>17</v>
-      </c>
-      <c r="D27" t="s">
-        <v>414</v>
-      </c>
-      <c r="E27" t="s">
-        <v>237</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" t="s">
+        <v>393</v>
+      </c>
+      <c r="I28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" t="s">
         <v>440</v>
       </c>
-      <c r="G27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" t="s">
-        <v>35</v>
-      </c>
-      <c r="I27" t="s">
-        <v>392</v>
-      </c>
-      <c r="J27" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="28" spans="3:10">
-      <c r="C28" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" t="s">
-        <v>415</v>
-      </c>
-      <c r="E28" t="s">
-        <v>237</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="D29" t="s">
+        <v>237</v>
+      </c>
+      <c r="E29" t="s">
         <v>441</v>
       </c>
-      <c r="G28" t="s">
-        <v>25</v>
-      </c>
-      <c r="H28" t="s">
-        <v>35</v>
-      </c>
-      <c r="I28" t="s">
-        <v>392</v>
-      </c>
-      <c r="J28" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="29" spans="3:10">
-      <c r="C29" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" t="s">
-        <v>416</v>
-      </c>
-      <c r="E29" t="s">
-        <v>237</v>
-      </c>
       <c r="F29" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" t="s">
+        <v>393</v>
+      </c>
+      <c r="I29" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
         <v>442</v>
       </c>
-      <c r="G29" t="s">
-        <v>25</v>
-      </c>
-      <c r="H29" t="s">
-        <v>35</v>
-      </c>
-      <c r="I29" t="s">
-        <v>392</v>
-      </c>
-      <c r="J29" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="30" spans="3:10">
-      <c r="C30" t="s">
-        <v>17</v>
-      </c>
       <c r="D30" t="s">
-        <v>417</v>
+        <v>237</v>
       </c>
       <c r="E30" t="s">
-        <v>237</v>
+        <v>443</v>
       </c>
       <c r="F30" t="s">
-        <v>443</v>
+        <v>25</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H30" t="s">
-        <v>35</v>
+        <v>393</v>
       </c>
       <c r="I30" t="s">
-        <v>392</v>
-      </c>
-      <c r="J30" t="s">
         <v>241</v>
       </c>
     </row>

--- a/VerveStacks_FRA_grids_kan25/SysSettings.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC27E40-D542-4407-9376-32DC514A3EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D013217C-8AD1-4F02-8474-A40D3C8C0968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6223,7 +6223,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEB30AB0-9DED-4762-9CEF-0BA57B65D439}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF69A6D6-F795-4CFC-913D-B1F027CE6DC3}">
   <dimension ref="B3:I30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_FRA_grids_kan25/SysSettings.xlsx
+++ b/VerveStacks_FRA_grids_kan25/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_FRA_grids_kan25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D013217C-8AD1-4F02-8474-A40D3C8C0968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69F8D63C-7A7F-41CF-8F83-B3748C6D3E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6223,7 +6223,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF69A6D6-F795-4CFC-913D-B1F027CE6DC3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0186BA-A01C-4B03-85B1-D16BF0837B5C}">
   <dimension ref="B3:I30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
